--- a/Matrix.xlsx
+++ b/Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\my_project\python\AHP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A468973-6FF7-4082-A9F0-FF60CC38ABC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A319A8D6-494F-4DEA-9702-78FFC64B6851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,34 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="20">
-  <si>
-    <t>Phim</t>
-  </si>
-  <si>
-    <t>Avengers</t>
-  </si>
-  <si>
-    <t>Vùng Đất Linh Hồn</t>
-  </si>
-  <si>
-    <t>The Thing</t>
-  </si>
-  <si>
-    <t>Interstellar</t>
-  </si>
-  <si>
-    <t>Squid Game</t>
-  </si>
-  <si>
-    <t>Toy Story</t>
-  </si>
-  <si>
-    <t>Lật Mặt 7</t>
-  </si>
-  <si>
-    <t>Avengers: Endgame</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="12">
   <si>
     <t>1</t>
   </si>
@@ -60,38 +33,41 @@
     <t>3</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>1/3</t>
   </si>
   <si>
     <t>1/2</t>
   </si>
   <si>
-    <t>1/5</t>
-  </si>
-  <si>
-    <t>1/4</t>
-  </si>
-  <si>
-    <t>1/6</t>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t>Thể loại</t>
+  </si>
+  <si>
+    <t>Đánh giá IMDb</t>
+  </si>
+  <si>
+    <t>Thời lượng</t>
+  </si>
+  <si>
+    <t>Đạo diễn</t>
+  </si>
+  <si>
+    <t>Đề cử &amp; Giải thưởng</t>
+  </si>
+  <si>
+    <t>Quốc gia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,8 +88,21 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,8 +121,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -143,16 +138,42 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -160,16 +181,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,226 +493,209 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="G7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Matrix.xlsx
+++ b/Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\my_project\python\AHP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A319A8D6-494F-4DEA-9702-78FFC64B6851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07CBC19-D189-402D-B261-221485C2AF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -138,42 +138,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -181,36 +155,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -493,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
@@ -507,175 +473,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="11" t="s">
+      <c r="B2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="11" t="s">
+      <c r="E2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="B3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="C4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="11" t="s">
+      <c r="D6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11" t="s">
+      <c r="F6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="12" t="s">
+      <c r="B7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -685,7 +651,7 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
+      <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -694,9 +660,6 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="3"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
